--- a/reports/report_IntegerOverflowTest.sol.xlsx
+++ b/reports/report_IntegerOverflowTest.sol.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-20 14:29:13</t>
+          <t>2026-04-05 19:37:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
